--- a/ascend-memory-table/scripts/template.xlsx
+++ b/ascend-memory-table/scripts/template.xlsx
@@ -549,7 +549,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>全局 num_key_value_heads；TP 后 Hkv_local=max(1,Hkv//TP) [HF config / vLLM MiniMax TP]</t>
+          <t>全局 num_key_value_heads；TP 后 Hkv_local=max(1,Hkv//TP)；MLA(DeepSeek) 不使用 Hkv（用 kv_lora_rank）[HF config / vLLM TP]</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>config.head_dim [HF config]</t>
+          <t>config.head_dim；DeepSeek MLA 无此字段（用 qk_nope+qk_rope / v_head_dim）[HF config]</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>L × 2 × Hkv_local × D × dtype [AttentionSpec.real_page_size_bytes / block_size]</t>
+          <t>GQA: L × 2 × Hkv_local × D × dtype；MLA(DeepSeek): L × (kv_lora_rank+qk_rope_head_dim) × dtype（无 ×2）[AttentionSpec.real_page_size_bytes / block_size]</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>MTP/EAGLE draft 层 KV；无 MTP 权重 / 未开 speculative → 0 [vllm/v1/spec_decode]</t>
+          <t>MTP/NextN/EAGLE draft 层 KV = draft_layers × per_layer_main_kv；无 draft → 0 [vllm/v1/spec_decode]</t>
         </is>
       </c>
     </row>

--- a/ascend-memory-table/scripts/template.xlsx
+++ b/ascend-memory-table/scripts/template.xlsx
@@ -549,7 +549,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>全局 num_key_value_heads；TP 后 Hkv_local=max(1,Hkv//TP)；MLA(DeepSeek) 不使用 Hkv（用 kv_lora_rank）[HF config / vLLM TP]</t>
+          <t>【运行时按模型生成】GQA: Hkv_local=max(1,Hkv//TP)；MLA: 不使用 Hkv [AttentionSpec / MLAAttentionSpec]</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KV/Index dtype 字节；BF16=2，C8/INT8=1 [CacheConfig.cache_dtype → get_dtype_size]</t>
+          <t>KV/Index dtype 字节；BF16=2，C8/INT8=1；自动判定见 formulas.md §I [CacheConfig.cache_dtype → get_dtype_size]</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>config.num_local_experts [HF config]</t>
+          <t>num_experts / num_local_experts / n_routed_experts（按系列归一化）[HF config]</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>num_experts // EP [推导]</t>
+          <t>【运行时按模型生成】num_experts // EP；dense → 0 [MoE EP 分片]</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EP=TP×DP（开 --enable-expert-parallel）[vllm/distributed; vLLM-Ascend MoE EP]</t>
+          <t>【运行时按模型生成】EP=TP×DP（开 --enable-expert-parallel）否则 EP=TP [vllm/distributed; vLLM-Ascend MoE EP]</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>model_runner.model_memory_usage（实测）；理论 W8A8 见行39 [worker.py::load_model]</t>
+          <t>【运行时按模型生成】实测 model_runner.model_memory_usage / 理论 W8A8 见行39 [worker.py::load_model]</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>available_kv = requested − (W + peak_act + non_torch) ※不含 graph [worker.py:581]</t>
+          <t>【运行时按模型生成】available_kv = requested − (W + peak_act + non_torch) ※不含 graph [worker.py:581]</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>requested − (W + peak_act + non_torch + graph) − 150MiB [worker.py:720,728]</t>
+          <t>【运行时按模型生成】requested − (W + peak_act + non_torch + graph) − 150MiB [worker.py:720,728]</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>init_free − (W + peak_act + non_torch + graph) − 150MiB [worker.py:729]</t>
+          <t>【运行时按模型生成】init_free − (W + peak_act + non_torch + graph) − 150MiB [worker.py:729]</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>available_kv // page // layers（hybrid 时 // max(L,L_sparse)）；page=2·block·Hkv_local·D·dtype [kv_cache_utils.py:1009 get_num_blocks; :1380]</t>
+          <t>【运行时按模型生成】avail//page//effective_layers；GQA page=2·block·Hkv_local·D·dtype；MLA page=block·(kv_lora+qk_rope)·dtype [kv_cache_utils.py:1009,1380]</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>num_blocks / blocks_per_req；blocks_per_req=Σ cdiv(max_model_len, group.block_size) [kv_cache_utils.py:951,958]</t>
+          <t>【运行时按模型生成】num_blocks / blocks_per_req [kv_cache_utils.py:951,958]</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       <c r="B38" s="4" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>计算公式（vLLM / vLLM-Ascend 源码口径）</t>
+          <t>计算公式（vLLM / vLLM-Ascend 源码口径；公式按模型架构动态生成）</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>W8A8 = K_emb_lm/TP·2 + K_norms·2 + K_gate·4 + (Q_attn[+Q_dense+Q_shared+Q_idx])/TP·1 + Q_experts/EP·1 [worker.py + 推导]</t>
+          <t>【运行时按模型生成】按架构分项：emb/TP·2 + norms·2 + gate·4 + attn/TP + [dense/TP] + [shared/TP] + [indexer/TP] + experts/EP [worker.py + 推导]</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>requested − W − act − non_torch（= 行29）[worker.py:581]</t>
+          <t>【运行时按模型生成】= 行29 [worker.py:581]</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GQA: L × 2 × Hkv_local × D × dtype；MLA(DeepSeek): L × (kv_lora_rank+qk_rope_head_dim) × dtype（无 ×2）[AttentionSpec.real_page_size_bytes / block_size]</t>
+          <t>【运行时按模型生成】GQA: L×2×Hkv_local×D×dtype；MLA: L×(kv_lora_rank+qk_rope_head_dim)×dtype（无 ×2）[AttentionSpec / MLAAttentionSpec]</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>L_sparse × 1 × IdxD × dtype（key-only，无 ×2）[MLAAttentionSpec; indexer.py:161]</t>
+          <t>【运行时按模型生成】L_sparse×1×IdxD×dtype（key-only，无 ×2）；无 indexer → 0 [MLAAttentionSpec; indexer.py:161]</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>MTP/NextN/EAGLE draft 层 KV = draft_layers × per_layer_main_kv；无 draft → 0 [vllm/v1/spec_decode]</t>
+          <t>【运行时按模型生成】draft_layers×per_layer_main_kv；无 draft → 0 [vllm/v1/spec_decode]</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>main + index + draft（每卡口径，已含 TP 分片）[推导]</t>
+          <t>【运行时按模型生成】main + index + draft（每卡口径，含 TP 分片）[推导]</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>max_concurrency × max_model_len（= 行34）[kv_cache_utils.py:1833]</t>
+          <t>【运行时按模型生成】max_concurrency × max_model_len（= 行34）[kv_cache_utils.py:1833]</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>(available_kv / sum_bytes_per_token) / B [kv_cache_utils.py:958]</t>
+          <t>【运行时按模型生成】(available_kv / sum_bytes_per_token) / B [kv_cache_utils.py:958]</t>
         </is>
       </c>
     </row>
